--- a/weights.xlsx
+++ b/weights.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E104"/>
+  <dimension ref="A1:E118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.7109375" customWidth="1" min="1" max="1"/>
@@ -2001,6 +2001,246 @@
         <v>201.2</v>
       </c>
       <c r="C104" t="inlineStr">
+        <is>
+          <t>Marat</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>208.2</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>15.53</v>
+      </c>
+      <c r="E105" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>180</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Marat</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>203.6</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>15.53</v>
+      </c>
+      <c r="E107" t="n">
+        <v>39.5</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>177</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Marat</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>180.6</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Marat</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>204</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>15.38</v>
+      </c>
+      <c r="E110" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>203.6</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>15.24</v>
+      </c>
+      <c r="E111" t="n">
+        <v>39.75</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>184.2</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Marat</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>208.9</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>15.82</v>
+      </c>
+      <c r="E113" t="n">
+        <v>39.75</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>211</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>212.7</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>184</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Marat</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>182.6</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Marat</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>181</v>
+      </c>
+      <c r="C118" t="inlineStr">
         <is>
           <t>Marat</t>
         </is>

--- a/weights.xlsx
+++ b/weights.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E118"/>
+  <dimension ref="A1:E146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.7109375" customWidth="1" min="1" max="1"/>
@@ -2243,6 +2243,474 @@
       <c r="C118" t="inlineStr">
         <is>
           <t>Marat</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>208.5</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>17.27</v>
+      </c>
+      <c r="E119" t="n">
+        <v>40.5</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Marat</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>211.4</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>183.6</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Marat</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>207.1</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>183</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Marat</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>203.4</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>16.11</v>
+      </c>
+      <c r="E125" t="n">
+        <v>39.75</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>184.1</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Marat</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>199.7</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>14.57</v>
+      </c>
+      <c r="E127" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>182.2</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Marat</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>201.9</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="E129" t="n">
+        <v>38.5</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>183</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Marat</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>199.3</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>13.15</v>
+      </c>
+      <c r="E131" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>184</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Marat</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>198.2</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>12.97</v>
+      </c>
+      <c r="E133" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>184</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Marat</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>205.2</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>13.45</v>
+      </c>
+      <c r="E135" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>182.4</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Marat</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>211.3</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>15.53</v>
+      </c>
+      <c r="E137" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>182</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Marat</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>209.7</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>184</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Marat</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>212.3</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>209</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>184</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Marat</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>181.2</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Marat</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>183.2</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Marat</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>210.4</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Michael</t>
         </is>
       </c>
     </row>
